--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -3307,17 +3307,23 @@
       <c r="N35" s="2" t="n">
         <v>46036</v>
       </c>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26132000000248578441_北京理工大学_20260126150712 (1).pdf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>无匹配</t>
+          <t>完美匹配</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4034,26 +4040,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26322000000606455461_北京理工大学_20260123172814 (1).pdf</t>
+          <t>D:\发票\报销中\dzfp_26132000000248578441_北京理工大学_20260126150712 (1).pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>300</v>
+        <v>1856</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>电子发票（普通发票） 发票号码：26322000000606455461 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：宿迁罗百电子有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91321322MAEMB52RX0 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征收率</t>
+          <t>电子发票（普通发票） 发票号码：26132000000248578441 开票日期：2026年01月26日 购 名称：北京理工大学 销 名称：廊坊腾仕仪器有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91131003MAD84HLY8R 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征收率</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3182012725409827840</t>
+          <t>3183772585941827584</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -4063,26 +4069,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
+          <t>D:\发票\报销中\dzfp_26322000000606455461_北京理工大学_20260123172814 (1).pdf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>300</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>电子发票（普通发票） 发票号码：26442000000861348616 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：广州毅修科技有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440101MA9XR3FY2R 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征收率</t>
+          <t>电子发票（普通发票） 发票号码：26322000000606455461 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：宿迁罗百电子有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91321322MAEMB52RX0 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征收率</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3184297068295827456</t>
+          <t>3182012725409827840</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -4092,26 +4098,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>电子发票（普通发票） 发票号码：26442000000861537901 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：佛山市奥维度贸易有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440605MA4UUCYUXF 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征</t>
+          <t>电子发票（普通发票） 发票号码：26442000000861348616 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：广州毅修科技有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440101MA9XR3FY2R 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征收率</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3187035950928827392</t>
+          <t>3184297068295827456</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -4121,26 +4127,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>电子发票（普通发票） 发票号码：26442000000884644516 开票日期：2026年01月24日 购 名称：北京理工大学 销 名称：东莞市德力欧精密设备有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91441900MABU9Q389Y 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
+          <t>电子发票（普通发票） 发票号码：26442000000861537901 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：佛山市奥维度贸易有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440605MA4UUCYUXF 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3184297068296827392</t>
+          <t>3187035950928827392</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -4150,29 +4156,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>47.4</v>
+        <v>248</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
+          <t>电子发票（普通发票） 发票号码：26442000000884644516 开票日期：2026年01月24日 购 名称：北京理工大学 销 名称：东莞市德力欧精密设备有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91441900MABU9Q389Y 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>32</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3184297068296827392</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>电子发票（普通发票） 发票号码：26952000000311180191 开票日期：2026年01月26日 购 名称：北京理工大学 销 名称：深圳市华锦益五金制品有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440300MA5GN0PM5U 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>8</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>3178635204870827520</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4187,7 +4222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4785,32 +4820,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26322000000606455461_北京理工大学_20260123172814 (1).pdf</t>
+          <t>D:\发票\报销中\dzfp_26132000000248578441_北京理工大学_20260126150712 (1).pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>300</v>
+        <v>1856</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3182012725409827840</t>
+          <t>3183772585941827584</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>300</v>
+        <v>1856</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>罗百电子</t>
+          <t>朗齐旗舰店</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -4825,32 +4860,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
+          <t>D:\发票\报销中\dzfp_26322000000606455461_北京理工大学_20260123172814 (1).pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>300</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3184297068295827456</t>
+          <t>3182012725409827840</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>300</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>毅修科技工具</t>
+          <t>罗百电子</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -4865,32 +4900,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3187035950928827392</t>
+          <t>3184297068295827456</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>奥维度五金</t>
+          <t>毅修科技工具</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4905,32 +4940,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3184297068296827392</t>
+          <t>3187035950928827392</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>德力欧网印商城</t>
+          <t>奥维度五金</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -4945,32 +4980,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>47.4</v>
+        <v>248</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3178635204870827520</t>
+          <t>3184297068296827392</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>47.4</v>
+        <v>248</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46033</v>
+        <v>46036</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>中通达螺丝五金</t>
+          <t>德力欧网印商城</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -4985,46 +5020,86 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\378594A_20260126_13352410 (1).pdf</t>
+          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>859.4400000000001</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>46048</v>
-      </c>
+        <v>47.4</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3178635204870827520</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>中通达螺丝五金</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\378594A_20260126_13352410 (1).pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>859.4400000000001</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
         <v>36</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H21" t="n">
         <v>859.4400000000001</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="I21" s="2" t="n">
         <v>46034</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>嘉立创</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>0.8833333333333333</v>
       </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5098,7 +5173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6465,26 +6540,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3183772585941827584</t>
+          <t>3179697747085827584</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>朗齐旗舰店</t>
+          <t>必兴金属</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>【优惠价】朗齐手机维修显微镜4K高清双目三目高清体视连续变倍7-50倍LED光源主板焊接珠宝鉴定放大镜 (三目大平板7-100倍+4800万像素相机接电脑和显示器拍照录像) x1 | 朗齐显微镜偏振光源环形灯手机电子维修专用灯LED亮度可调高端看金属检测消除防止过滤反光偏光防眩光 (高亮LED偏光光源（上下偏振片 消除反光）) x1</t>
+          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=711854459624&amp;mi_id=0000xB4Q0pChFMgP_Snvil6SKuVayNJqM3-2VD34AoDNIRA</t>
+          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1856</v>
+        <v>60</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -6493,30 +6568,30 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3183772585941827584</t>
+          <t>3179697747085827584</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>朗齐旗舰店</t>
+          <t>必兴金属</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>【优惠价】朗齐手机维修显微镜4K高清双目三目高清体视连续变倍7-50倍LED光源主板焊接珠宝鉴定放大镜 (三目大平板7-100倍+4800万像素相机接电脑和显示器拍照录像) x1 | 朗齐显微镜偏振光源环形灯手机电子维修专用灯LED亮度可调高端看金属检测消除防止过滤反光偏光防眩光 (高亮LED偏光光源（上下偏振片 消除反光）) x1</t>
+          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1856</v>
+        <v>60</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=711854459624&amp;mi_id=0000xB4Q0pChFMgP_Snvil6SKuVayNJqM3-2VD34AoDNIRA</t>
+          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -6525,7 +6600,7 @@
         </is>
       </c>
       <c r="N18" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -6541,85 +6616,6 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>3179697747085827584</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>必兴金属</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>60</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>交易成功</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>3179697747085827584</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>必兴金属</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>60</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>交易成功</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>未找到匹配发票</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -2074,17 +2074,23 @@
       <c r="N20" s="2" t="n">
         <v>46044</v>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26322000000682369516_北京理工大学_20260126174337.pdf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>无匹配</t>
+          <t>完美匹配</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4098,26 +4104,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
+          <t>D:\发票\报销中\dzfp_26322000000682369516_北京理工大学_20260126174337.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>485</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>电子发票（普通发票） 发票号码：26442000000861348616 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：广州毅修科技有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440101MA9XR3FY2R 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征收率</t>
+          <t>电子发票（普通发票） 发票号码：26322000000682369516 开票日期：2026年01月26日 购 名称：北京理工大学 销 名称：苏州市金阊区墨工基业仪器商行 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：420822198911144563 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3184297068295827456</t>
+          <t>3200811564282827776</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -4127,26 +4133,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>电子发票（普通发票） 发票号码：26442000000861537901 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：佛山市奥维度贸易有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440605MA4UUCYUXF 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征</t>
+          <t>电子发票（普通发票） 发票号码：26442000000861348616 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：广州毅修科技有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440101MA9XR3FY2R 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征收率</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3187035950928827392</t>
+          <t>3184297068295827456</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -4156,26 +4162,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>电子发票（普通发票） 发票号码：26442000000884644516 开票日期：2026年01月24日 购 名称：北京理工大学 销 名称：东莞市德力欧精密设备有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91441900MABU9Q389Y 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
+          <t>电子发票（普通发票） 发票号码：26442000000861537901 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：佛山市奥维度贸易有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440605MA4UUCYUXF 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3184297068296827392</t>
+          <t>3187035950928827392</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -4185,29 +4191,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>47.4</v>
+        <v>248</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
+          <t>电子发票（普通发票） 发票号码：26442000000884644516 开票日期：2026年01月24日 购 名称：北京理工大学 销 名称：东莞市德力欧精密设备有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91441900MABU9Q389Y 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>32</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3184297068296827392</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>电子发票（普通发票） 发票号码：26952000000311180191 开票日期：2026年01月26日 购 名称：北京理工大学 销 名称：深圳市华锦益五金制品有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440300MA5GN0PM5U 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>8</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>3178635204870827520</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4222,7 +4257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4900,32 +4935,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
+          <t>D:\发票\报销中\dzfp_26322000000682369516_北京理工大学_20260126174337.pdf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>485</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3184297068295827456</t>
+          <t>3200811564282827776</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>485</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46036</v>
+        <v>46044</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>毅修科技工具</t>
+          <t>ETA淘宝总店</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4940,32 +4975,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3187035950928827392</t>
+          <t>3184297068295827456</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>奥维度五金</t>
+          <t>毅修科技工具</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -4980,32 +5015,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3184297068296827392</t>
+          <t>3187035950928827392</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>德力欧网印商城</t>
+          <t>奥维度五金</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -5020,32 +5055,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
+          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>47.4</v>
+        <v>248</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3178635204870827520</t>
+          <t>3184297068296827392</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>47.4</v>
+        <v>248</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46033</v>
+        <v>46036</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>中通达螺丝五金</t>
+          <t>德力欧网印商城</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -5060,46 +5095,86 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\378594A_20260126_13352410 (1).pdf</t>
+          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>859.4400000000001</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>46048</v>
-      </c>
+        <v>47.4</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3178635204870827520</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>中通达螺丝五金</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\378594A_20260126_13352410 (1).pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>859.4400000000001</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
         <v>36</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="H22" t="n">
         <v>859.4400000000001</v>
       </c>
-      <c r="I21" s="2" t="n">
+      <c r="I22" s="2" t="n">
         <v>46034</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>嘉立创</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>0.8833333333333333</v>
       </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
         <v>0.5333333333333333</v>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5173,7 +5248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5987,26 +6062,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3200811564282827776</t>
+          <t>3199723971509827584</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETA淘宝总店</t>
+          <t>迅维网深圳店</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>埃塔ETA2217顶针测试治具SMD贴片元件LCR电桥测试电容电感测试夹 (ETA2217) x1</t>
+          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=748128257059&amp;mi_id=0000K4eQuEVHOIHrJGamuGfOToJDl0BySW0Fs298OAFysTU</t>
+          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x0qGTd1YA3DQzhuKh0eQQD4</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>485</v>
+        <v>1330</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -6020,25 +6095,25 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3200811564282827776</t>
+          <t>3199723971509827584</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ETA淘宝总店</t>
+          <t>迅维网深圳店</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>埃塔ETA2217顶针测试治具SMD贴片元件LCR电桥测试电容电感测试夹 (ETA2217) x1</t>
+          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>485</v>
+        <v>1330</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=748128257059&amp;mi_id=0000K4eQuEVHOIHrJGamuGfOToJDl0BySW0Fs298OAFysTU</t>
+          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x0qGTd1YA3DQzhuKh0eQQD4</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -6066,26 +6141,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3199723971509827584</t>
+          <t>3199604882263827456</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>迅维网深圳店</t>
+          <t>明翔科技通讯店</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1</t>
+          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x0qGTd1YA3DQzhuKh0eQQD4</t>
+          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTuiWigvxnbJiHfK_CcERvIk</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1330</v>
+        <v>19.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -6099,25 +6174,25 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3199723971509827584</t>
+          <t>3199604882263827456</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>迅维网深圳店</t>
+          <t>明翔科技通讯店</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1</t>
+          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1330</v>
+        <v>19.6</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x0qGTd1YA3DQzhuKh0eQQD4</t>
+          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTuiWigvxnbJiHfK_CcERvIk</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -6145,26 +6220,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3199604882263827456</t>
+          <t>3196898943024827392</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>明翔科技通讯店</t>
+          <t>文宇创新</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2</t>
+          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTuiWigvxnbJiHfK_CcERvIk</t>
+          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI_MDFeZjV8NPXqAFG5PjQ7Q</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>19.6</v>
+        <v>103</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6173,30 +6248,30 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3199604882263827456</t>
+          <t>3196898943024827392</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>明翔科技通讯店</t>
+          <t>文宇创新</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2</t>
+          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>19.6</v>
+        <v>103</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTuiWigvxnbJiHfK_CcERvIk</t>
+          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI_MDFeZjV8NPXqAFG5PjQ7Q</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6205,7 +6280,7 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>46044</v>
+        <v>46042</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -6224,26 +6299,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3196898943024827392</t>
+          <t>3196645358892827648</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>文宇创新</t>
+          <t>维修佬旗舰店</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1</t>
+          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI_MDFeZjV8NPXqAFG5PjQ7Q</t>
+          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LXhyS72BQvbcR4MccYMdlbA</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103</v>
+        <v>18.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -6257,25 +6332,25 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3196898943024827392</t>
+          <t>3196645358892827648</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>文宇创新</t>
+          <t>维修佬旗舰店</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1</t>
+          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>103</v>
+        <v>18.2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI_MDFeZjV8NPXqAFG5PjQ7Q</t>
+          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LXhyS72BQvbcR4MccYMdlbA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6303,26 +6378,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3196645358892827648</t>
+          <t>3186970539401827840</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>维修佬旗舰店</t>
+          <t>强森实业广东有限公司1企业店</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1</t>
+          <t>高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;1.0mm) x1 | 高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;0.5mm) x1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LXhyS72BQvbcR4MccYMdlbA</t>
+          <t>https://item.taobao.com/item.htm?id=757313939071&amp;mi_id=0000schi65QYLVIfJeUrNLJmihl5G9u4ZVOctZqL-qiDiBs</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>18.2</v>
+        <v>99.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -6331,30 +6406,30 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3196645358892827648</t>
+          <t>3186970539401827840</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>维修佬旗舰店</t>
+          <t>强森实业广东有限公司1企业店</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1</t>
+          <t>高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;1.0mm) x1 | 高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;0.5mm) x1</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>18.2</v>
+        <v>99.8</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LXhyS72BQvbcR4MccYMdlbA</t>
+          <t>https://item.taobao.com/item.htm?id=757313939071&amp;mi_id=0000schi65QYLVIfJeUrNLJmihl5G9u4ZVOctZqL-qiDiBs</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6363,7 +6438,7 @@
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>46042</v>
+        <v>46038</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -6382,26 +6457,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3186970539401827840</t>
+          <t>3184297068282827776</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>强森实业广东有限公司1企业店</t>
+          <t>维修佬旗舰店</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;1.0mm) x1 | 高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;0.5mm) x1</t>
+          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=757313939071&amp;mi_id=0000schi65QYLVIfJeUrNLJmihl5G9u4ZVOctZqL-qiDiBs</t>
+          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb3yligO3qeTIyKrLLRc83V0</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>99.8</v>
+        <v>134.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -6410,30 +6485,30 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3186970539401827840</t>
+          <t>3184297068282827776</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>强森实业广东有限公司1企业店</t>
+          <t>维修佬旗舰店</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;1.0mm) x1 | 高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;0.5mm) x1</t>
+          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>99.8</v>
+        <v>134.6</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=757313939071&amp;mi_id=0000schi65QYLVIfJeUrNLJmihl5G9u4ZVOctZqL-qiDiBs</t>
+          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb3yligO3qeTIyKrLLRc83V0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -6442,7 +6517,7 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -6461,26 +6536,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3184297068282827776</t>
+          <t>3179697747085827584</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>维修佬旗舰店</t>
+          <t>必兴金属</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3</t>
+          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb3yligO3qeTIyKrLLRc83V0</t>
+          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>134.6</v>
+        <v>60</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -6489,30 +6564,30 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3184297068282827776</t>
+          <t>3179697747085827584</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>维修佬旗舰店</t>
+          <t>必兴金属</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3</t>
+          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>134.6</v>
+        <v>60</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb3yligO3qeTIyKrLLRc83V0</t>
+          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -6521,7 +6596,7 @@
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>46036</v>
+        <v>46034</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -6537,85 +6612,6 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3179697747085827584</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>必兴金属</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>60</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>交易成功</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>3179697747085827584</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>必兴金属</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>60</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>交易成功</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>未找到匹配发票</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -433,66 +433,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>product_link</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>order_status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>order_date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>_order_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>_vendor</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>_description</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>_amount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>_product_link</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>_status</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>_vendor</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>_description</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>_product_link</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>_status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>_match_invoice_file</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>_match_invoice_id</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>_match_score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>_match_status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>_match_reason</t>
         </is>
@@ -501,246 +536,399 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3202958352610827776</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>166</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>46045</v>
+          <t>3179189569859827564</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>北京格上电子</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>全新原装 电子元器件一站式采购配单 电子元件配单 BOM配套采购 (暂无) x636</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>广陆旗舰店</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>【优惠价】广陆原点数显卡尺0-150-200-300数字电子不锈钢工业文玩油标包邮 (原点0-150mm（塑胶壳+金属面板）) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=37807787594&amp;mi_id=0000A2ezMl5odpAyK_TuES19aTFQ1DlIa1GRmNSTtb-WZqc</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>636</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=39422439278&amp;mi_id=0000JKnj5PwfY00JnuLgVBHoPr0AsF1tt3X46NG-abw7qtM</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>买家已付款</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3179189569859827564</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>北京格上电子</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>全新原装 电子元器件一站式采购配单 电子元件配单 BOM配套采购 (暂无) x636</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>636</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=37807787594&amp;mi_id=0000A2ezMl5odpAyK_TuES19aTFQ1DlIa1GRmNSTtb-WZqc</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\20260113dzfp_26112000000152209486_北京理工大学_20260113105440.pdf</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3202334979020827648</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>174</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>46045</v>
+          <t>3178679736231827564</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>极博星电子科技直销店铺</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>极博星T12手柄快插型休眠座休眠高品质 (适用于245休眠座休眠6针插头（不包含发热芯）) x1 | C245C210C115T12恒温曲线焊台极博星GEEBOON维修电烙铁超203/936 (TC22_SSD01_245+210套件) x1</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>博一电子</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.04*12345689000股 丝包线 多股丝包线 利兹线高频线 纱包线纯铜 (0.04X1200股/1米) x30.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=704751302614&amp;mi_id=0000Efst4r6KOsZoPGeYmqNlc6HDevst_suWkmMS1tLe2_A</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>376.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=573902310960&amp;mi_id=00006UB_SshtKVung6Rk-n4FipRvRFBBv8Zr_Ih7SaSA4ro</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\26322000000657341491-北京理工大学.pdf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3178679736231827564</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>极博星电子科技直销店铺</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>极博星T12手柄快插型休眠座休眠高品质 (适用于245休眠座休眠6针插头（不包含发热芯）) x1 | C245C210C115T12恒温曲线焊台极博星GEEBOON维修电烙铁超203/936 (TC22_SSD01_245+210套件) x1</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>376.6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=704751302614&amp;mi_id=0000Efst4r6KOsZoPGeYmqNlc6HDevst_suWkmMS1tLe2_A</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3202216358786827776</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>327.32</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>46045</v>
+          <t>3178549561194827564</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>深圳市优信电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FFC/FPC软排线 液晶连接线 6P 同向/反向 0.5/1.0mm间距 (6P;同向;0．5mm;20CM) x4 | FFC/FPC软排线 液晶连接线 6P 同向/反向 0.5/1.0mm间距 (6P;同向;0．5mm;40CM) x4</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>拓竹官方旗舰店</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>拓竹 热床刮刀刀片 3D打印机配件 (热床刮刀刀片) x1.0 | 【会员专享】拓竹3D打印配件 单件6折起 限时抢购 (固体胶3支装（单支到手6折）) x1.0 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光炭黑11101【含料盘】) x1.0 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光草绿11500【含料盘】) x1.0 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光冰蓝11601【含料盘】) x1.0 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光橘橙11300【含料盘】) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=549515372213&amp;mi_id=0000TONxVuzfDqqsCnApxkm0wSEI72r53AXGsDeREaZJC0U</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3.58</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=694046419538&amp;mi_id=00000n-IWOfuOCd0XsVGexNIYX4GACtsDq8VAGRTgER5P1s</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\8-设备费-327.32元-深圳拓竹科技有限公司-2026.01.26-发票.pdf</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3178549561194827564</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>深圳市优信电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FFC/FPC软排线 液晶连接线 6P 同向/反向 0.5/1.0mm间距 (6P;同向;0．5mm;20CM) x4 | FFC/FPC软排线 液晶连接线 6P 同向/反向 0.5/1.0mm间距 (6P;同向;0．5mm;40CM) x4</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>3.58</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=549515372213&amp;mi_id=0000TONxVuzfDqqsCnApxkm0wSEI72r53AXGsDeREaZJC0U</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3202216358793827840</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>274.8</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>46045</v>
+          <t>3178635204854827564</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>卓悦电子让工作轻松一点点</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>细颗粒高流动性焊锡膏0402贴片qfn小封装专用强力SMT微粒含挤锡器 (套件(专用锡膏+挤锡器+6针头)) x2</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>polymaker旗舰店</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (白色) x1.0 | 【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (彩虹渐变) x1.0 | 【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (冰系渐变) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=695056092174&amp;mi_id=00009HGazowYq_yqiQH9SoYTI00dZCksDsg8xfoVxJFaUT8</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=930515916047&amp;mi_id=0000nY6biu1Rr_Gn6NTrYB1Or6Mk5s3zjsbEDpM_0_BNzOg</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\3202216358793827564_263220000006_66203971.pdf</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3178635204854827564</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>卓悦电子让工作轻松一点点</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>细颗粒高流动性焊锡膏0402贴片qfn小封装专用强力SMT微粒含挤锡器 (套件(专用锡膏+挤锡器+6针头)) x2</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=695056092174&amp;mi_id=00009HGazowYq_yqiQH9SoYTI00dZCksDsg8xfoVxJFaUT8</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3200362430879827456</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>46044</v>
+          <t>3178635204855827564</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>康威科技</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AD637模块有效值检波检测模块 峰值电压检测模块交流信号数据采集 (暂无) x1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>乐清铜业</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>紫铜皮紫铜带纯紫铜薄铜箔片接地导电铜板铜带片紫铜垫片0.02-1mm (0.15mm*30mm*1米) x5.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=521661938898&amp;mi_id=0000vVe5H0E13hY2dJ_hy-yNhFpLIpFrB0LBkR1v7P-gbUs</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>124</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=698854826005&amp;mi_id=0000T8iwLtHJEokThYL-3-G5ouGIZyzvkmiPiSWnYaYuun0</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3178635204855827564</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>康威科技</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>AD637模块有效值检波检测模块 峰值电压检测模块交流信号数据采集 (暂无) x1</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>124</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=521661938898&amp;mi_id=0000vVe5H0E13hY2dJ_hy-yNhFpLIpFrB0LBkR1v7P-gbUs</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -749,378 +937,660 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3200811564282827776</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>485</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>46044</v>
+          <t>3178635204856827564</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>电子采购中心</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>适用泰克鼎阳优利德示波器探头接地弹簧接地圈针示波器探头接地环 (内径4.5mm  1个) x6 | 适用泰克鼎阳优利德示波器探头接地弹簧接地圈针示波器探头接地环 (内径3.5mm  1个) x6</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ETA淘宝总店</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>埃塔ETA2217顶针测试治具SMD贴片元件LCR电桥测试电容电感测试夹 (ETA2217) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=577099962185&amp;mi_id=0000BP1iumJ-537GbcyawyXszrp8KMi-oVJQ-AOdRg9abMg</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=748128257059&amp;mi_id=0000K4eQuEVHOIHrJGamuGfOTrlYGXjSbCiMRKlSnC69uiE</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26322000000682369516_北京理工大学_20260126174337.pdf</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3178635204856827564</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>电子采购中心</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>适用泰克鼎阳优利德示波器探头接地弹簧接地圈针示波器探头接地环 (内径4.5mm  1个) x6 | 适用泰克鼎阳优利德示波器探头接地弹簧接地圈针示波器探头接地环 (内径3.5mm  1个) x6</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>12</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=577099962185&amp;mi_id=0000BP1iumJ-537GbcyawyXszrp8KMi-oVJQ-AOdRg9abMg</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3199723971509827584</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1330</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>46044</v>
+          <t>3178635204859827564</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>特加特数码专营店</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.4m;灰色 4代 IPEX单头线) x5 | 4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.1m;灰色 4代 IPEX单头线) x5 | 4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.2m;灰色 4代 IPEX单头线) x5 | 4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.2m;4代IPEX转SMA 内螺内针) x5 | 4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.4m;4代IPEX转SMA 内螺内针) x5</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>迅维网深圳店</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=558125856203&amp;mi_id=0000NKZGqTboQIKFznokyDpfz7h2KDFjQnOoj97h8TvvG0s</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x3nIQTq9ptt71miLGzzMj10</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3178635204859827564</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>特加特数码专营店</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.4m;灰色 4代 IPEX单头线) x5 | 4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.1m;灰色 4代 IPEX单头线) x5 | 4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.2m;灰色 4代 IPEX单头线) x5 | 4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.2m;4代IPEX转SMA 内螺内针) x5 | 4代ipex转SMA外螺内孔线 mini网卡M2天线接口转接线UFL四代测试线 (0.4m;4代IPEX转SMA 内螺内针) x5</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=558125856203&amp;mi_id=0000NKZGqTboQIKFznokyDpfz7h2KDFjQnOoj97h8TvvG0s</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\7-设备费-82.10元-深圳市特加特科技有限公司-2026.01.24-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3200239884180827648</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1478</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>46044</v>
+          <t>3178635204865827564</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>亿胜电子</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>贴片电阻本电容本0201 0402 0603 0805 1206电阻包电容包样品本 (村田0603电容本90种各50个) x1 | 贴片电阻本电容本0201 0402 0603 0805 1206电阻包电容包样品本 (村田0402电容本80种各50个) x1 | 贴片电阻本电容本0201 0402 0603 0805 1206电阻包电容包样品本 (国巨0603电阻本170种1%各50个) x1 | 贴片电阻本电容本0201 0402 0603 0805 1206电阻包电容包样品本 (国巨0402电阻本170种1%各50个) x1</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>杭州睿登科技</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源供应器 (RD6030-MAX(3.2寸2000W前级)整机) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=576391131079&amp;mi_id=0000mMiQoW0NqjaA-vbvmq8FTqTuVSEYEeXNTmfv98lc3zM</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>134.9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=781265244038&amp;mi_id=0000hbfxm3fykFbXojRRB075xjIyttyMzCLWRbSNTBQJUZA</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>交易关闭</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3178635204865827564</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>亿胜电子</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>贴片电阻本电容本0201 0402 0603 0805 1206电阻包电容包样品本 (村田0603电容本90种各50个) x1 | 贴片电阻本电容本0201 0402 0603 0805 1206电阻包电容包样品本 (村田0402电容本80种各50个) x1 | 贴片电阻本电容本0201 0402 0603 0805 1206电阻包电容包样品本 (国巨0603电阻本170种1%各50个) x1 | 贴片电阻本电容本0201 0402 0603 0805 1206电阻包电容包样品本 (国巨0402电阻本170种1%各50个) x1</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>134.9</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=576391131079&amp;mi_id=0000mMiQoW0NqjaA-vbvmq8FTqTuVSEYEeXNTmfv98lc3zM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\5-设备费-134.90元-深圳市创发胜电子有限公司-2026.01.23-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3199604882263827456</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>46044</v>
+          <t>3178635204870827564</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>中通达螺丝五金</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>镀金铜片粒电池USB导电极PCB散热圆方形垫片SMD焊接贴片铜块触点 (方形6*1*厚0.5（20个）) x1 | 镀金铜片粒电池USB导电极PCB散热圆方形垫片SMD焊接贴片铜块触点 (方形8*1*厚0.5（10个）) x2 | 镀金铜片粒电池USB导电极PCB散热圆方形垫片SMD焊接贴片铜块触点 (方形5*2*厚0.8（20个）) x2 | 镀金铜片粒电池USB导电极PCB散热圆方形垫片SMD焊接贴片铜块触点 (方形5*3*厚0.8（20个）) x3</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>明翔科技通讯店</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=675732787142&amp;mi_id=00008-wcpMuz33SGuYyZWZ7GxcXND4fmOY2hkxNOu_qn-gQ</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>47.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTvCt68DBJy_B0qVJMhPZRzg</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3178635204870827564</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>中通达螺丝五金</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>镀金铜片粒电池USB导电极PCB散热圆方形垫片SMD焊接贴片铜块触点 (方形6*1*厚0.5（20个）) x1 | 镀金铜片粒电池USB导电极PCB散热圆方形垫片SMD焊接贴片铜块触点 (方形8*1*厚0.5（10个）) x2 | 镀金铜片粒电池USB导电极PCB散热圆方形垫片SMD焊接贴片铜块触点 (方形5*2*厚0.8（20个）) x2 | 镀金铜片粒电池USB导电极PCB散热圆方形垫片SMD焊接贴片铜块触点 (方形5*3*厚0.8（20个）) x3</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>47.4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=675732787142&amp;mi_id=00008-wcpMuz33SGuYyZWZ7GxcXND4fmOY2hkxNOu_qn-gQ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3196898943024827392</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>103</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>46042</v>
+          <t>3178635204875827564</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>镇江市美凌电子有限公司</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>台式万用表笔硅胶线万能表笔线万用表笔特尖特细针多功能组合1908 (18-1-1（1米直弯198芯）) x1</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>文宇创新</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=607683595007&amp;mi_id=00000ucNnwuN9cneOUch9s79cRGwzaDybOZ8GorAeto9DCc</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>82.66</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI-dnfBScWixz827TuA_MieI</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3178635204875827564</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>镇江市美凌电子有限公司</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>台式万用表笔硅胶线万能表笔线万用表笔特尖特细针多功能组合1908 (18-1-1（1米直弯198芯）) x1</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>82.66</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=607683595007&amp;mi_id=00000ucNnwuN9cneOUch9s79cRGwzaDybOZ8GorAeto9DCc</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\1-设备费-82.66元-扬中市琪悦通讯器材经营部（个体工商户）-2026.01.23-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3196645358892827648</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>46042</v>
+          <t>3169736652059827564</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>宝钢电子smt激光钢网制造</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SMT钢网钢片专业激光精密定做打样PCB钢网刷锡膏红胶LED灯条钢网 (小钢片10*10CM无框) x1</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>维修佬旗舰店</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=45847270670&amp;mi_id=0000f2QudEjVq1FNKJc-Oi_INVEkvD5BStYyYi8aMpE93qM</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>22</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LfwojNceyOdm3vrTghNC2aA</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3169736652059827564</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>宝钢电子smt激光钢网制造</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>SMT钢网钢片专业激光精密定做打样PCB钢网刷锡膏红胶LED灯条钢网 (小钢片10*10CM无框) x1</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>22</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=45847270670&amp;mi_id=0000f2QudEjVq1FNKJc-Oi_INVEkvD5BStYyYi8aMpE93qM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\4-其他-22.00元-中山市东凤镇一振钢网加工店-2026.01.23-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3195467077463827456</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>37.85</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>46041</v>
+          <t>3169468165118827564</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>协达兴科技</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>电子元器件配套 BOM表配单 阻容感管芯连接器电子元件一站式配单 (暂无) x430</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>绿林官方旗舰店</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>绿林自动剥线钳新款多功能钳子工业级拨线剪线钳电工专用工具大全 (【剥线免调节】多功能剥线钳【分线绕线】) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=714251628632&amp;mi_id=00009GTbPxqfcoqZwolE8i4SW_G-uUXUdms4S6wZfhAFDQY</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>435</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=957841310262&amp;mi_id=0000Z7aO3iZzE7vmKm70QSCR_5bVePSJbdhwoQ7l8FPWisw</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\2-其他-37.85元-烟台市绿林工具有限公司-2026.01.23-发票.pdf</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3169468165118827564</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>协达兴科技</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>电子元器件配套 BOM表配单 阻容感管芯连接器电子元件一站式配单 (暂无) x430</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>435</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=714251628632&amp;mi_id=00009GTbPxqfcoqZwolE8i4SW_G-uUXUdms4S6wZfhAFDQY</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3191044839501827584</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>46040</v>
+          <t>3208342657476827564</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>恒脉PDU华中总店</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>加长10位12位16位PDU工业工程专用20位24超长插线板机柜插排插座 (16位【双断+防雷】2.5平方2米10A头[新国标孔]) x1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>七哥化妆品  护肤品</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>欧莱雅男士水能保湿酷爽水凝露50ml*3瓶=150ml爽肤水补水正品小样 (250ml[5瓶  27年后]) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=806839670595&amp;mi_id=00003CKKu17BY8_WER8IyWYTn6D_wLQc9dg1qEuv-joxpxg</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>183</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=683617811077&amp;mi_id=0000rnIdNferFF2YOxDVZS6Fq8k7oXM82GA-nV2wLj-4CbQ</t>
+          <t>买家已付款</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3208342657476827564</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>恒脉PDU华中总店</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>加长10位12位16位PDU工业工程专用20位24超长插线板机柜插排插座 (16位【双断+防雷】2.5平方2米10A头[新国标孔]) x1</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>183</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=806839670595&amp;mi_id=00003CKKu17BY8_WER8IyWYTn6D_wLQc9dg1qEuv-joxpxg</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>买家已付款</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -1129,148 +1599,247 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3191372760939827712</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>27</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>46039</v>
+          <t>3202958352610827564</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>广陆旗舰店</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>【优惠价】广陆原点数显卡尺0-150-200-300数字电子不锈钢工业文玩油标包邮 (原点0-150mm（塑胶壳+金属面板）) x1</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>付鑫科技</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>水口钳子工业级超硬斜嘴钳子电子模型钳斜口钳电工专用偏口钳子 (（超薄超尖）5寸水口钳 CR-V) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=39422439278&amp;mi_id=0000JKnj5PwfY00JnuLgVBHoPgq231e-T32L4h8ZxYynCqU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>166</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=800389722309&amp;mi_id=0000OEPaAekB7Rq2deYUdnRrOV4GoLIt5YqALyUDtnJVJZo</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\6-其他-27.00元-河间市祺暖五金制品有限公司-2026.01.24-发票.pdf</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3202958352610827564</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>广陆旗舰店</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>【优惠价】广陆原点数显卡尺0-150-200-300数字电子不锈钢工业文玩油标包邮 (原点0-150mm（塑胶壳+金属面板）) x1</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>166</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=39422439278&amp;mi_id=0000JKnj5PwfY00JnuLgVBHoPgq231e-T32L4h8ZxYynCqU</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3188060403141827584</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>46038</v>
+          <t>3202334979020827564</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>博一电子</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.04*12345689000股 丝包线 多股丝包线 利兹线高频线 纱包线纯铜 (0.04X1200股/1米) x30</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>思壮伟业运动专营店</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>李宁运动保暖发带耳罩冬季男防寒防风护耳护额骑车跑步耳朵保护套 (☀️凛冬推荐☀️加厚针织款【耳罩/眼罩/发带三合一】) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=573902310960&amp;mi_id=00006UB_SshtKVung6Rk-n4Fit8IZhJi8CmrZlqwQCl83sc</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>174</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=990037011548&amp;mi_id=0000VWKJmd5zBM5cexYafT3v_cf0EzAzO48Hztou0RPob_I</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3202334979020827564</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>博一电子</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.04*12345689000股 丝包线 多股丝包线 利兹线高频线 纱包线纯铜 (0.04X1200股/1米) x30</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>174</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=573902310960&amp;mi_id=00006UB_SshtKVung6Rk-n4Fit8IZhJi8CmrZlqwQCl83sc</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\26322000000657341491-北京理工大学.pdf</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3187035950928827392</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>81</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>46038</v>
+          <t>3202216358786827564</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>拓竹官方旗舰店</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>拓竹 热床刮刀刀片 3D打印机配件 (热床刮刀刀片) x1 | 【会员专享】拓竹3D打印配件 单件6折起 限时抢购 (固体胶3支装（单支到手6折）) x1 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光炭黑11101【含料盘】) x1 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光草绿11500【含料盘】) x1 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光冰蓝11601【含料盘】) x1 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光橘橙11300【含料盘】) x1</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>奥维度五金</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜8x8x5mm;无导热胶纸) x10.0 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜8x8x5mm;带进口3M公司8810胶纸) x10.0 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜10x14x5mm;无导热胶纸) x4.0 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜10x14x5mm;带进口3M公司8810胶纸) x4.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=694046419538&amp;mi_id=00000n-IWOfuOCd0XsVGexNIYXkhQ3zIJrMl_12YaVEiFgQ</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>327.32</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=737677427613&amp;mi_id=0000YG_nDPpAV-LhWAn-E4P9utK51sRsBK0FuVQQWk-H6ug</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
+          <t>3202216358786827564</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>拓竹官方旗舰店</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>拓竹 热床刮刀刀片 3D打印机配件 (热床刮刀刀片) x1 | 【会员专享】拓竹3D打印配件 单件6折起 限时抢购 (固体胶3支装（单支到手6折）) x1 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光炭黑11101【含料盘】) x1 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光草绿11500【含料盘】) x1 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光冰蓝11601【含料盘】) x1 | 拓竹PLA Matte哑光 3D打印耗材 高韧性易剥离高速易打印 RFID智能参数识别 (哑光橘橙11300【含料盘】) x1</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>327.32</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=694046419538&amp;mi_id=00000n-IWOfuOCd0XsVGexNIYXkhQ3zIJrMl_12YaVEiFgQ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\8-设备费-327.32元-深圳拓竹科技有限公司-2026.01.26-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>完美匹配</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>金额一致且唯一匹配</t>
         </is>
@@ -1279,50 +1848,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3186970539401827840</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>46038</v>
+          <t>3202216358793827564</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>polymaker旗舰店</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (白色) x1 | 【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (彩虹渐变) x1 | 【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (冰系渐变) x1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>强森实业广东有限公司1企业店</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;1.0mm) x1.0 | 高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;0.5mm) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=930515916047&amp;mi_id=0000nY6biu1Rr_Gn6NTrYB1OrylfWjmQUu-wYDc2l-z5dg8</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>274.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=757313939071&amp;mi_id=0000schi65QYLVIfJeUrNLJmipzPiV7yN9i0ljVWqo39R-4</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000946232656_北京理工大学_20260126155824.pdf</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr">
+          <t>3202216358793827564</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>polymaker旗舰店</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (白色) x1 | 【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (彩虹渐变) x1 | 【优惠价】[新品] Polymaker HT-PLA 耐高温PLA HT-PLA-GF 3d打印机耗材 类ABS无需 (冰系渐变) x1</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=930515916047&amp;mi_id=0000nY6biu1Rr_Gn6NTrYB1OrylfWjmQUu-wYDc2l-z5dg8</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\3202216358793827564_263220000006_66203971.pdf</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>完美匹配</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>金额一致且唯一匹配</t>
         </is>
@@ -1331,102 +1933,162 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3185082195776827392</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>114</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>46037</v>
+          <t>3200362430879827564</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>乐清铜业</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>紫铜皮紫铜带纯紫铜薄铜箔片接地导电铜板铜带片紫铜垫片0.02-1mm (0.15mm*30mm*1米) x5</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>北京格上电子</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>全新原装 电子元器件一站式采购配单 电子元件配单 BOM配套采购 (暂无) x114.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=698854826005&amp;mi_id=0000T8iwLtHJEokThYL-3-G5or8sQH3KmSyT4JO_yB7cUHs</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>28</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=37807787594&amp;mi_id=0000A2ezMl5odpAyK_TuES19aWVQLPUpmlOPVy_vpHx1IRc</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\20260116dzfp_26112000000197079406_北京理工大学_20260116094718.pdf</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3200362430879827564</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>乐清铜业</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>紫铜皮紫铜带纯紫铜薄铜箔片接地导电铜板铜带片紫铜垫片0.02-1mm (0.15mm*30mm*1米) x5</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>28</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=698854826005&amp;mi_id=0000T8iwLtHJEokThYL-3-G5or8sQH3KmSyT4JO_yB7cUHs</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3184574883584827392</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>309</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>46036</v>
+          <t>3200811564282827564</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ETA淘宝总店</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>埃塔ETA2217顶针测试治具SMD贴片元件LCR电桥测试电容电感测试夹 (ETA2217) x1</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>博一电子</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.04*12345689000股 丝包线 多股丝包线 利兹线高频线 纱包线纯铜 (0.04X3000股/1米) x20.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=748128257059&amp;mi_id=0000K4eQuEVHOIHrJGamuGfOToJDl0BySW0Fs298OAFysTU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>485</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=573902310960&amp;mi_id=00006UB_SshtKVung6Rk-n4FipRvRFBBv8Zr_Ih7SaSA4ro</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\26322000000610527901-北京理工大学.pdf</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr">
+          <t>3200811564282827564</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ETA淘宝总店</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>埃塔ETA2217顶针测试治具SMD贴片元件LCR电桥测试电容电感测试夹 (ETA2217) x1</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>485</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=748128257059&amp;mi_id=0000K4eQuEVHOIHrJGamuGfOToJDl0BySW0Fs298OAFysTU</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26322000000682369516_北京理工大学_20260126174337.pdf</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>完美匹配</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>金额一致且唯一匹配</t>
         </is>
@@ -1435,44 +2097,77 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3184297068282827776</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>134.6</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>46036</v>
+          <t>3199723971509827564</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>迅维网深圳店</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>维修佬旗舰店</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1.0 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1.0 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1.0 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1.0 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1.0 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x0qGTd1YA3DQzhuKh0eQQD4</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1330</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb9mvNJZv120vXB3vHOCK8KE</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3199723971509827564</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>迅维网深圳店</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1330</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x0qGTd1YA3DQzhuKh0eQQD4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -1481,206 +2176,320 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3184297068289827840</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>139.9</v>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>46036</v>
+          <t>3199604882263827564</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>明翔科技通讯店</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>鹿仙子旗舰店</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>【优惠价】鹿仙子紫外线固化灯数显无线UV胶绿油美甲手机维修led紫光大功率 (【插电款】5W大芯片固化灯) x1.0 | 鹿仙子美工金属雕刻刀套装手工刀片手机维修斜口陶瓷笔刀加厚工具 (折叠美工刀+【23号】刀片*10) x1.0 | 【优惠价】鹿仙子1007电子线焊接维修导线连接线镀锡铜30AWG电子设备配线 (16AWG电子线【镀锡铜线芯】共25米/盒) x1.0 | 【优惠价】鹿仙子1007电子线焊接维修导线连接线镀锡铜30AWG电子设备配线 (28AWG电子线【镀锡铜线芯】共100米/盒) x1.0 | 鹿仙子烙铁高温海绵焊接锡焊清理专用烙铁头清洁器电烙铁垫清洗棉 (长方形（5片装）独立袋装) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTuiWigvxnbJiHfK_CcERvIk</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>19.6</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=847065252870&amp;mi_id=0000IVxhOR2yTxFHRXy8facCOjQSmgL5u5gmPRIvEuCRnOM</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\3-其他-139.90元-深圳大恩时电子科技有限公司-2026.01.23-发票.pdf</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3199604882263827564</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>明翔科技通讯店</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>19.6</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTuiWigvxnbJiHfK_CcERvIk</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3184297068295827456</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>94</v>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>46036</v>
+          <t>3196898943024827564</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>文宇创新</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>毅修科技工具</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2UUL×WYLIE联合出品羽神Ti11钛合金镊子超精密特硬特尖飞线镊子 (Ti11钛合金镊子（直）) x2.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI_MDFeZjV8NPXqAFG5PjQ7Q</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=633779808516&amp;mi_id=0000N0HzqiQzHecb3WwasQUQ17WniBJZvxxnq_YG7Ngd3Tw</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>交易成功</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3196898943024827564</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>文宇创新</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>103</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI_MDFeZjV8NPXqAFG5PjQ7Q</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3184297068296827392</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>248</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>46036</v>
+          <t>3196645358892827564</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>维修佬旗舰店</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>德力欧网印商城</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>pcb钢网印刷台钢网锡膏印刷台印刷机丝印台smt手动印刷台刷锡台 (15_15涨紧款_) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LXhyS72BQvbcR4MccYMdlbA</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>18.2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=945595509148&amp;mi_id=00000SJGV3pTe0gjoxkFXttbQf0qyU71a9p0cdZQ9ospLLA</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>完美匹配</t>
-        </is>
+          <t>3196645358892827564</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>维修佬旗舰店</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>18.2</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>金额一致且唯一匹配</t>
+          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LXhyS72BQvbcR4MccYMdlbA</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3183772585941827584</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1856</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>46036</v>
+          <t>3195467077463827564</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>绿林官方旗舰店</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>绿林自动剥线钳新款多功能钳子工业级拨线剪线钳电工专用工具大全 (【剥线免调节】多功能剥线钳【分线绕线】) x1</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>朗齐旗舰店</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>【优惠价】朗齐手机维修显微镜4K高清双目三目高清体视连续变倍7-50倍LED光源主板焊接珠宝鉴定放大镜 (三目大平板7-100倍+4800万像素相机接电脑和显示器拍照录像) x1.0 | 朗齐显微镜偏振光源环形灯手机电子维修专用灯LED亮度可调高端看金属检测消除防止过滤反光偏光防眩光 (高亮LED偏光光源（上下偏振片 消除反光）) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=957841310262&amp;mi_id=0000Z7aO3iZzE7vmKm70QSCR_21xnpkFBb2xaoth_ebKTA4</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>37.85</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=711854459624&amp;mi_id=0000xB4Q0pChFMgP_Snvil6SKkLv0gyC63sfZPIIHIBN-Rk</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26132000000248578441_北京理工大学_20260126150712 (1).pdf</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" t="inlineStr">
+          <t>3195467077463827564</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>绿林官方旗舰店</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>绿林自动剥线钳新款多功能钳子工业级拨线剪线钳电工专用工具大全 (【剥线免调节】多功能剥线钳【分线绕线】) x1</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=957841310262&amp;mi_id=0000Z7aO3iZzE7vmKm70QSCR_21xnpkFBb2xaoth_ebKTA4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\2-其他-37.85元-烟台市绿林工具有限公司-2026.01.23-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>完美匹配</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>金额一致且唯一匹配</t>
         </is>
@@ -1689,50 +2498,83 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3182012725409827840</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>300</v>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>46035</v>
+          <t>3191372760939827564</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>付鑫科技</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>水口钳子工业级超硬斜嘴钳子电子模型钳斜口钳电工专用偏口钳子 (（超薄超尖）5寸水口钳 CR-V) x1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>罗百电子</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>无线充/变压器/铁氧体磁芯定制开发免开模快速雕刻出样 (铁氧体1(拍前请联系客服)) x15.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=800389722309&amp;mi_id=0000OEPaAekB7Rq2deYUdnRrOW_gs2s4hN3Crz4wMG4pz8E</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>27</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=975098737604&amp;mi_id=0000wy97ZL5DbbL8mUJmXC6Ye7oPTTv_uAcx67Eh-bRspYQ</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26322000000606455461_北京理工大学_20260123172814 (1).pdf</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="inlineStr">
+          <t>3191372760939827564</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>付鑫科技</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>水口钳子工业级超硬斜嘴钳子电子模型钳斜口钳电工专用偏口钳子 (（超薄超尖）5寸水口钳 CR-V) x1</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>27</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=800389722309&amp;mi_id=0000OEPaAekB7Rq2deYUdnRrOW_gs2s4hN3Crz4wMG4pz8E</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>46039</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\6-其他-27.00元-河间市祺暖五金制品有限公司-2026.01.24-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>完美匹配</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>金额一致且唯一匹配</t>
         </is>
@@ -1741,96 +2583,168 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3179697747085827584</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>60</v>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>46034</v>
+          <t>3187035950928827564</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>奥维度五金</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜8x8x5mm;无导热胶纸) x10 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜8x8x5mm;带进口3M公司8810胶纸) x10 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜10x14x5mm;无导热胶纸) x4 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜10x14x5mm;带进口3M公司8810胶纸) x4</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>必兴金属</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=737677427613&amp;mi_id=0000YG_nDPpAV-LhWAn-E4P9uhBKGeTuTaIA3lsT4Bu2pCE</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>81</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJZ-vVMgEkIXfYBOzCAlTnNM</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3187035950928827564</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>奥维度五金</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜8x8x5mm;无导热胶纸) x10 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜8x8x5mm;带进口3M公司8810胶纸) x10 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜10x14x5mm;无导热胶纸) x4 | 带胶可选  6mm -30mm 微型纯铜散热片 芯片、显存、内存 MOS散热 (紫铜10x14x5mm;带进口3M公司8810胶纸) x4</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>81</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=737677427613&amp;mi_id=0000YG_nDPpAV-LhWAn-E4P9uhBKGeTuTaIA3lsT4Bu2pCE</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3179189569859827712</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>636</v>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>46034</v>
+          <t>3186970539401827564</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>强森实业广东有限公司1企业店</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;1.0mm) x1 | 高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;0.5mm) x1</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>北京格上电子</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>全新原装 电子元器件一站式采购配单 电子元件配单 BOM配套采购 (暂无) x636.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=757313939071&amp;mi_id=0000schi65QYLVIfJeUrNLJmihl5G9u4ZVOctZqL-qiDiBs</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>99.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=37807787594&amp;mi_id=0000A2ezMl5odpAyK_TuES19aWVQLPUpmlOPVy_vpHx1IRc</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>交易成功</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\20260113dzfp_26112000000152209486_北京理工大学_20260113105440.pdf</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="inlineStr">
+          <t>3186970539401827564</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>强森实业广东有限公司1企业店</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;1.0mm) x1 | 高导热硅胶片18W氮化铝显卡显存软PCB板固态硬盘散热垫MOS管IGBT (18.6W/m.k超高导热[氮化铝配方];100*200mm;0.5mm) x1</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=757313939071&amp;mi_id=0000schi65QYLVIfJeUrNLJmihl5G9u4ZVOctZqL-qiDiBs</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26442000000946232656_北京理工大学_20260126155824.pdf</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>完美匹配</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>金额一致且唯一匹配</t>
         </is>
@@ -1839,138 +2753,838 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3178956756098827776</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>46034</v>
+          <t>3185082195776827564</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>北京格上电子</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>全新原装 电子元器件一站式采购配单 电子元件配单 BOM配套采购 (暂无) x114</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>生产电源厂家</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>220V转DC12V24V1A2A1.5A2A3A4A5ALED灯带电源适配器变压器 带开关 (12V1A（电源）1米线+带开关) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=37807787594&amp;mi_id=0000A2ezMl5odpAyK_TuES19aTw5TqGDgr5lbxb6_7uPM5Q</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>114</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=708700312757&amp;mi_id=00004xBCQx384xSrpK17M3PLveisSeCKgCKdqmPR2EZOaGU</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>交易成功</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3185082195776827564</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>北京格上电子</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>全新原装 电子元器件一站式采购配单 电子元件配单 BOM配套采购 (暂无) x114</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>114</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=37807787594&amp;mi_id=0000A2ezMl5odpAyK_TuES19aTw5TqGDgr5lbxb6_7uPM5Q</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\20260116dzfp_26112000000197079406_北京理工大学_20260116094718.pdf</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3178953012990827520</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>46034</v>
+          <t>3184574883584827564</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>博一电子</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.04*12345689000股 丝包线 多股丝包线 利兹线高频线 纱包线纯铜 (0.04X3000股/1米) x20</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>大西洋科技视讯99</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>12V红外补光灯监控红外辅助灯大功率红外灯智能光感阵列4灯辅助灯 (12v 4灯红外常亮单独补光灯) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=573902310960&amp;mi_id=00006UB_SshtKVung6Rk-n4Fit8IZhJi8CmrZlqwQCl83sc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=538753635277&amp;mi_id=0000Vxky2MZksjR4DaXBHq__5Elwt7APDIpzh7gETbta5zc</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>交易成功</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>无匹配</t>
-        </is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3184574883584827564</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>博一电子</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.04*12345689000股 丝包线 多股丝包线 利兹线高频线 纱包线纯铜 (0.04X3000股/1米) x20</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>309</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>未找到匹配发票</t>
+          <t>https://item.taobao.com/item.htm?id=573902310960&amp;mi_id=00006UB_SshtKVung6Rk-n4Fit8IZhJi8CmrZlqwQCl83sc</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\26322000000610527901-北京理工大学.pdf</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3178830181591827456</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="C31" s="2" t="n">
+          <t>3184297068282827564</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>维修佬旗舰店</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb3yligO3qeTIyKrLLRc83V0</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3184297068282827564</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>维修佬旗舰店</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb3yligO3qeTIyKrLLRc83V0</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3184297068289827564</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>鹿仙子旗舰店</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>【优惠价】鹿仙子紫外线固化灯数显无线UV胶绿油美甲手机维修led紫光大功率 (【插电款】5W大芯片固化灯) x1 | 鹿仙子美工金属雕刻刀套装手工刀片手机维修斜口陶瓷笔刀加厚工具 (折叠美工刀+【23号】刀片*10) x1 | 【优惠价】鹿仙子1007电子线焊接维修导线连接线镀锡铜30AWG电子设备配线 (16AWG电子线【镀锡铜线芯】共25米/盒) x1 | 【优惠价】鹿仙子1007电子线焊接维修导线连接线镀锡铜30AWG电子设备配线 (28AWG电子线【镀锡铜线芯】共100米/盒) x1 | 鹿仙子烙铁高温海绵焊接锡焊清理专用烙铁头清洁器电烙铁垫清洗棉 (长方形（5片装）独立袋装) x1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=847065252870&amp;mi_id=0000IVxhOR2yTxFHRXy8facCOmEte69eS6pYwskv9UmHJJo</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3184297068289827564</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>鹿仙子旗舰店</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>【优惠价】鹿仙子紫外线固化灯数显无线UV胶绿油美甲手机维修led紫光大功率 (【插电款】5W大芯片固化灯) x1 | 鹿仙子美工金属雕刻刀套装手工刀片手机维修斜口陶瓷笔刀加厚工具 (折叠美工刀+【23号】刀片*10) x1 | 【优惠价】鹿仙子1007电子线焊接维修导线连接线镀锡铜30AWG电子设备配线 (16AWG电子线【镀锡铜线芯】共25米/盒) x1 | 【优惠价】鹿仙子1007电子线焊接维修导线连接线镀锡铜30AWG电子设备配线 (28AWG电子线【镀锡铜线芯】共100米/盒) x1 | 鹿仙子烙铁高温海绵焊接锡焊清理专用烙铁头清洁器电烙铁垫清洗棉 (长方形（5片装）独立袋装) x1</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=847065252870&amp;mi_id=0000IVxhOR2yTxFHRXy8facCOmEte69eS6pYwskv9UmHJJo</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\3-其他-139.90元-深圳大恩时电子科技有限公司-2026.01.23-发票.pdf</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3184297068295827564</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>毅修科技工具</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2UUL×WYLIE联合出品羽神Ti11钛合金镊子超精密特硬特尖飞线镊子 (Ti11钛合金镊子（直）) x2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=633779808516&amp;mi_id=0000N0HzqiQzHecb3WwasQUQ14sCUMGxyN-Hx2IoNkajGn4</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>94</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3184297068295827564</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>毅修科技工具</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2UUL×WYLIE联合出品羽神Ti11钛合金镊子超精密特硬特尖飞线镊子 (Ti11钛合金镊子（直）) x2</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>94</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=633779808516&amp;mi_id=0000N0HzqiQzHecb3WwasQUQ14sCUMGxyN-Hx2IoNkajGn4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3184297068296827564</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>德力欧网印商城</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>pcb钢网印刷台钢网锡膏印刷台印刷机丝印台smt手动印刷台刷锡台 (15_15涨紧款_) x1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=945595509148&amp;mi_id=00000SJGV3pTe0gjoxkFXttbQf7ZW-EKetxqjQ51eAIR7bI</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>248</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3184297068296827564</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>德力欧网印商城</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>pcb钢网印刷台钢网锡膏印刷台印刷机丝印台smt手动印刷台刷锡台 (15_15涨紧款_) x1</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>248</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=945595509148&amp;mi_id=00000SJGV3pTe0gjoxkFXttbQf7ZW-EKetxqjQ51eAIR7bI</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3183772585941827564</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>朗齐旗舰店</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>【优惠价】朗齐手机维修显微镜4K高清双目三目高清体视连续变倍7-50倍LED光源主板焊接珠宝鉴定放大镜 (三目大平板7-100倍+4800万像素相机接电脑和显示器拍照录像) x1 | 朗齐显微镜偏振光源环形灯手机电子维修专用灯LED亮度可调高端看金属检测消除防止过滤反光偏光防眩光 (高亮LED偏光光源（上下偏振片 消除反光）) x1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=711854459624&amp;mi_id=0000xB4Q0pChFMgP_Snvil6SKuVayNJqM3-2VD34AoDNIRA</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1856</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>3183772585941827564</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>朗齐旗舰店</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>【优惠价】朗齐手机维修显微镜4K高清双目三目高清体视连续变倍7-50倍LED光源主板焊接珠宝鉴定放大镜 (三目大平板7-100倍+4800万像素相机接电脑和显示器拍照录像) x1 | 朗齐显微镜偏振光源环形灯手机电子维修专用灯LED亮度可调高端看金属检测消除防止过滤反光偏光防眩光 (高亮LED偏光光源（上下偏振片 消除反光）) x1</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1856</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=711854459624&amp;mi_id=0000xB4Q0pChFMgP_Snvil6SKuVayNJqM3-2VD34AoDNIRA</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26132000000248578441_北京理工大学_20260126150712 (1).pdf</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3182012725409827564</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>罗百电子</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>无线充/变压器/铁氧体磁芯定制开发免开模快速雕刻出样 (铁氧体1(拍前请联系客服)) x15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=975098737604&amp;mi_id=0000wy97ZL5DbbL8mUJmXC6YezflsOayo_rjoUkZNggpCa0</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>300</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3182012725409827564</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>罗百电子</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>无线充/变压器/铁氧体磁芯定制开发免开模快速雕刻出样 (铁氧体1(拍前请联系客服)) x15</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>300</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=975098737604&amp;mi_id=0000wy97ZL5DbbL8mUJmXC6YezflsOayo_rjoUkZNggpCa0</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26322000000606455461_北京理工大学_20260123172814 (1).pdf</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3179697747085827564</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>必兴金属</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3179697747085827564</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>必兴金属</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>60</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
         <v>46034</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>大西洋科技视讯99</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>12V红外补光灯监控红外辅助灯大功率红外灯智能光感阵列4灯辅助灯 (12v 4灯红外光感单独补光灯) x1.0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://item.taobao.com/item.htm?id=538753635277&amp;mi_id=0000Vxky2MZksjR4DaXBHq__5Elwt7APDIpzh7gETbta5zc</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>交易关闭</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>嘉立创</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>859.4400000000001</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>嘉立创</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>859.4400000000001</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\378594A_20260126_13352410 (1).pdf</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>完美匹配</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>金额一致且唯一匹配</t>
         </is>
       </c>
     </row>
@@ -2052,9 +3666,17 @@
           <t>电子发票（普通发票） 发票号码：26322000000606674641 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：扬中市琪悦通讯器材经营部（个体工商户） 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：92321182MADARYXN83 息 息 项目名称 规格型号 单 位 数 量 单 价 金</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3178635204875827564</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2074,11 +3696,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3195467077463827456</t>
+          <t>3195467077463827564</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -2103,11 +3725,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3179189569859827712</t>
+          <t>3179189569859827564</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -2132,11 +3754,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3185082195776827392</t>
+          <t>3185082195776827564</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -2161,11 +3783,11 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3184574883584827392</t>
+          <t>3184574883584827564</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -2190,11 +3812,11 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3202334979020827648</t>
+          <t>3202334979020827564</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -2219,11 +3841,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3184297068289827840</t>
+          <t>3184297068289827564</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -2248,11 +3870,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3202216358793827840</t>
+          <t>3202216358793827564</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -2278,9 +3900,17 @@
           <t>电子发票（普通发票） 发票号码:26957000000037029045 开票日期:2026年01月26日 购 销 名称:北京理工大学 名称:深圳嘉立创科技集团股份有限公司 买 售 方 方 信 信 统一社会信用代码/纳税人识别号:12100000400009127B 统一社会信用代码/纳税人识别号:91440300795432869Y 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2299,9 +3929,17 @@
           <t>电子发票（普通发票） 发票号码：26442000000868848856 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：中山市东凤镇一振钢网加工店 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：92442000MA52CRCK7T 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3169736652059827564</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2320,9 +3958,17 @@
           <t>电子发票（普通发票） 发票号码：26952000000293246791 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：深圳市创发胜电子有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440300MA5FFWQY23 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3178635204865827564</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2342,11 +3988,11 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3191372760939827712</t>
+          <t>3191372760939827564</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -2370,9 +4016,17 @@
           <t>电子发票（普通发票） 发票号码：26952000000298939546 开票日期：2026年01月24日 购 名称：北京理工大学 销 名称：深圳市特加特科技有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：914403000838768596 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3178635204859827564</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2392,11 +4046,11 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3202216358786827776</t>
+          <t>3202216358786827564</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -2421,11 +4075,11 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3183772585941827584</t>
+          <t>3183772585941827564</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -2450,11 +4104,11 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3182012725409827840</t>
+          <t>3182012725409827564</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2479,11 +4133,11 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3200811564282827776</t>
+          <t>3200811564282827564</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2508,11 +4162,11 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3184297068295827456</t>
+          <t>3184297068295827564</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -2537,11 +4191,11 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3187035950928827392</t>
+          <t>3187035950928827564</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -2566,11 +4220,11 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3184297068296827392</t>
+          <t>3184297068296827564</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2595,11 +4249,11 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3186970539401827840</t>
+          <t>3186970539401827564</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2623,9 +4277,17 @@
           <t>电子发票（普通发票） 发票号码：26952000000311180191 开票日期：2026年01月26日 购 名称：北京理工大学 销 名称：深圳市华锦益五金制品有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440300MA5GN0PM5U 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3178635204870827564</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2638,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2716,32 +4378,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\2-其他-37.85元-烟台市绿林工具有限公司-2026.01.23-发票.pdf</t>
+          <t>D:\发票\报销中\1-设备费-82.66元-扬中市琪悦通讯器材经营部（个体工商户）-2026.01.23-发票.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>37.85</v>
+        <v>82.66</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3195467077463827456</t>
+          <t>3178635204875827564</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>37.85</v>
+        <v>82.66</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46041</v>
+        <v>46033</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>绿林官方旗舰店</t>
+          <t>镇江市美凌电子有限公司</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -2756,32 +4418,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\20260113dzfp_26112000000152209486_北京理工大学_20260113105440.pdf</t>
+          <t>D:\发票\报销中\2-其他-37.85元-烟台市绿林工具有限公司-2026.01.23-发票.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>636</v>
+        <v>37.85</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3179189569859827712</t>
+          <t>3195467077463827564</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>636</v>
+        <v>37.85</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46034</v>
+        <v>46041</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>北京格上电子</t>
+          <t>绿林官方旗舰店</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -2796,28 +4458,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\20260116dzfp_26112000000197079406_北京理工大学_20260116094718.pdf</t>
+          <t>D:\发票\报销中\20260113dzfp_26112000000152209486_北京理工大学_20260113105440.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>636</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3185082195776827392</t>
+          <t>3179189569859827564</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>114</v>
+        <v>636</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46037</v>
+        <v>46034</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2836,32 +4498,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\26322000000610527901-北京理工大学.pdf</t>
+          <t>D:\发票\报销中\20260116dzfp_26112000000197079406_北京理工大学_20260116094718.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>309</v>
+        <v>114</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3184574883584827392</t>
+          <t>3185082195776827564</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>309</v>
+        <v>114</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>博一电子</t>
+          <t>北京格上电子</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -2876,28 +4538,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\26322000000657341491-北京理工大学.pdf</t>
+          <t>D:\发票\报销中\26322000000610527901-北京理工大学.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3202334979020827648</t>
+          <t>3184574883584827564</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2916,32 +4578,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\3-其他-139.90元-深圳大恩时电子科技有限公司-2026.01.23-发票.pdf</t>
+          <t>D:\发票\报销中\26322000000657341491-北京理工大学.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>139.9</v>
+        <v>174</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3184297068289827840</t>
+          <t>3202334979020827564</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>139.9</v>
+        <v>174</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46036</v>
+        <v>46045</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>鹿仙子旗舰店</t>
+          <t>博一电子</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -2956,32 +4618,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\3202216358793827564_263220000006_66203971.pdf</t>
+          <t>D:\发票\报销中\3-其他-139.90元-深圳大恩时电子科技有限公司-2026.01.23-发票.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>274.8</v>
+        <v>139.9</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3202216358793827840</t>
+          <t>3184297068289827564</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>274.8</v>
+        <v>139.9</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46045</v>
+        <v>46036</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>polymaker旗舰店</t>
+          <t>鹿仙子旗舰店</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -2996,32 +4658,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\6-其他-27.00元-河间市祺暖五金制品有限公司-2026.01.24-发票.pdf</t>
+          <t>D:\发票\报销中\3202216358793827564_263220000006_66203971.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>274.8</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3191372760939827712</t>
+          <t>3202216358793827564</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>27</v>
+        <v>274.8</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46039</v>
+        <v>46045</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>付鑫科技</t>
+          <t>polymaker旗舰店</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -3036,32 +4698,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\8-设备费-327.32元-深圳拓竹科技有限公司-2026.01.26-发票.pdf</t>
+          <t>D:\发票\报销中\378594A_20260126_13352410 (1).pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>327.32</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>859.4400000000001</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>46048</v>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3202216358786827776</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>327.32</v>
+        <v>859.4400000000001</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>拓竹官方旗舰店</t>
+          <t>嘉立创</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -3070,38 +4734,40 @@
       <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26132000000248578441_北京理工大学_20260126150712 (1).pdf</t>
+          <t>D:\发票\报销中\4-其他-22.00元-中山市东凤镇一振钢网加工店-2026.01.23-发票.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1856</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3183772585941827584</t>
+          <t>3169736652059827564</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1856</v>
+        <v>22</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>朗齐旗舰店</t>
+          <t>宝钢电子smt激光钢网制造</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -3116,32 +4782,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26322000000606455461_北京理工大学_20260123172814 (1).pdf</t>
+          <t>D:\发票\报销中\5-设备费-134.90元-深圳市创发胜电子有限公司-2026.01.23-发票.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>300</v>
+        <v>134.9</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3182012725409827840</t>
+          <t>3178635204865827564</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>300</v>
+        <v>134.9</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46035</v>
+        <v>46033</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>罗百电子</t>
+          <t>亿胜电子</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3156,32 +4822,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26322000000682369516_北京理工大学_20260126174337.pdf</t>
+          <t>D:\发票\报销中\6-其他-27.00元-河间市祺暖五金制品有限公司-2026.01.24-发票.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>485</v>
+        <v>27</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3200811564282827776</t>
+          <t>3191372760939827564</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>485</v>
+        <v>27</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46044</v>
+        <v>46039</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ETA淘宝总店</t>
+          <t>付鑫科技</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -3196,32 +4862,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
+          <t>D:\发票\报销中\7-设备费-82.10元-深圳市特加特科技有限公司-2026.01.24-发票.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3184297068295827456</t>
+          <t>3178635204859827564</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46036</v>
+        <v>46033</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>毅修科技工具</t>
+          <t>特加特数码专营店</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -3236,12 +4902,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
+          <t>D:\发票\报销中\8-设备费-327.32元-深圳拓竹科技有限公司-2026.01.26-发票.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>327.32</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
@@ -3250,18 +4916,18 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3187035950928827392</t>
+          <t>3202216358786827564</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>81</v>
+        <v>327.32</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>奥维度五金</t>
+          <t>拓竹官方旗舰店</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -3276,32 +4942,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
+          <t>D:\发票\报销中\dzfp_26132000000248578441_北京理工大学_20260126150712 (1).pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>248</v>
+        <v>1856</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3184297068296827392</t>
+          <t>3183772585941827564</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>248</v>
+        <v>1856</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>46036</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>德力欧网印商城</t>
+          <t>朗齐旗舰店</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -3316,32 +4982,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D:\发票\报销中\dzfp_26442000000946232656_北京理工大学_20260126155824.pdf</t>
+          <t>D:\发票\报销中\dzfp_26322000000606455461_北京理工大学_20260123172814 (1).pdf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>99.8</v>
+        <v>300</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3186970539401827840</t>
+          <t>3182012725409827564</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>99.8</v>
+        <v>300</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46038</v>
+        <v>46035</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>强森实业广东有限公司1企业店</t>
+          <t>罗百电子</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -3352,6 +5018,246 @@
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26322000000682369516_北京理工大学_20260126174337.pdf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>485</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3200811564282827564</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>485</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ETA淘宝总店</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26442000000861348616_广州毅修科技有限 公司_20260123172943.pdf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>94</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>31</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3184297068295827564</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>94</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>毅修科技工具</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26442000000861537901_佛山市奥维度贸易有 限公司_20260123173151.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>81</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>25</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3187035950928827564</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>81</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>奥维度五金</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26442000000884644516_东莞市德力欧精密设备有限公司_20260124161823.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>248</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>32</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3184297068296827564</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>248</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>德力欧网印商城</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\dzfp_26442000000946232656_北京理工大学_20260126155824.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>26</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3186970539401827564</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>强森实业广东有限公司1企业店</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3178635204870827564</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>中通达螺丝五金</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3364,7 +5270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3413,134 +5319,6 @@
           <t>match_score</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>D:\发票\报销中\1-设备费-82.66元-扬中市琪悦通讯器材经营部（个体工商户）-2026.01.23-发票.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>82.66</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>电子发票（普通发票） 发票号码：26322000000606674641 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：扬中市琪悦通讯器材经营部（个体工商户） 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：92321182MADARYXN83 息 息 项目名称 规格型号 单 位 数 量 单 价 金</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>D:\发票\报销中\378594A_20260126_13352410 (1).pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>859.4400000000001</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>46048</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>电子发票（普通发票） 发票号码:26957000000037029045 开票日期:2026年01月26日 购 销 名称:北京理工大学 名称:深圳嘉立创科技集团股份有限公司 买 售 方 方 信 信 统一社会信用代码/纳税人识别号:12100000400009127B 统一社会信用代码/纳税人识别号:91440300795432869Y 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>D:\发票\报销中\4-其他-22.00元-中山市东凤镇一振钢网加工店-2026.01.23-发票.pdf</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>电子发票（普通发票） 发票号码：26442000000868848856 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：中山市东凤镇一振钢网加工店 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：92442000MA52CRCK7T 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>D:\发票\报销中\5-设备费-134.90元-深圳市创发胜电子有限公司-2026.01.23-发票.pdf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>134.9</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>电子发票（普通发票） 发票号码：26952000000293246791 开票日期：2026年01月23日 购 名称：北京理工大学 销 名称：深圳市创发胜电子有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440300MA5FFWQY23 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>D:\发票\报销中\7-设备费-82.10元-深圳市特加特科技有限公司-2026.01.24-发票.pdf</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>电子发票（普通发票） 发票号码：26952000000298939546 开票日期：2026年01月24日 购 名称：北京理工大学 销 名称：深圳市特加特科技有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：914403000838768596 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率/征</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>D:\发票\报销中\其他-47.40元-深圳市华锦益五金制品有限公司-2026.01.26-发票.pdf</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>电子发票（普通发票） 发票号码：26952000000311180191 开票日期：2026年01月26日 购 名称：北京理工大学 销 名称：深圳市华锦益五金制品有限公司 买 售 方 方 信 统一社会信用代码/纳税人识别号：12100000400009127B 信 统一社会信用代码/纳税人识别号：91440300MA5GN0PM5U 息 息 项目名称 规格型号 单 位 数 量 单 价 金 额 税率</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3553,66 +5331,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>vendor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>product_link</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>order_status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>order_date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>_order_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>_vendor</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>_description</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>_amount</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>_product_link</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>_status</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>_date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>_vendor</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>_description</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>_product_link</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>_status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>_match_invoice_file</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>_match_invoice_id</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>_match_score</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>_match_status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>_match_reason</t>
         </is>
@@ -3621,44 +5434,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3202958352610827776</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>166</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>46045</v>
+          <t>3178679736231827564</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>极博星电子科技直销店铺</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>极博星T12手柄快插型休眠座休眠高品质 (适用于245休眠座休眠6针插头（不包含发热芯）) x1 | C245C210C115T12恒温曲线焊台极博星GEEBOON维修电烙铁超203/936 (TC22_SSD01_245+210套件) x1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>广陆旗舰店</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>【优惠价】广陆原点数显卡尺0-150-200-300数字电子不锈钢工业文玩油标包邮 (原点0-150mm（塑胶壳+金属面板）) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=704751302614&amp;mi_id=0000Efst4r6KOsZoPGeYmqNlc6HDevst_suWkmMS1tLe2_A</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>376.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=39422439278&amp;mi_id=0000JKnj5PwfY00JnuLgVBHoPr0AsF1tt3X46NG-abw7qtM</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>买家已付款</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3178679736231827564</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>极博星电子科技直销店铺</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>极博星T12手柄快插型休眠座休眠高品质 (适用于245休眠座休眠6针插头（不包含发热芯）) x1 | C245C210C115T12恒温曲线焊台极博星GEEBOON维修电烙铁超203/936 (TC22_SSD01_245+210套件) x1</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=704751302614&amp;mi_id=0000Efst4r6KOsZoPGeYmqNlc6HDevst_suWkmMS1tLe2_A</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -3667,44 +5513,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3200362430879827456</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>28</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>46044</v>
+          <t>3178549561194827564</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>深圳市优信电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FFC/FPC软排线 液晶连接线 6P 同向/反向 0.5/1.0mm间距 (6P;同向;0．5mm;20CM) x4 | FFC/FPC软排线 液晶连接线 6P 同向/反向 0.5/1.0mm间距 (6P;同向;0．5mm;40CM) x4</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>乐清铜业</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>紫铜皮紫铜带纯紫铜薄铜箔片接地导电铜板铜带片紫铜垫片0.02-1mm (0.15mm*30mm*1米) x5.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=549515372213&amp;mi_id=0000TONxVuzfDqqsCnApxkm0wSEI72r53AXGsDeREaZJC0U</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3.58</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=698854826005&amp;mi_id=0000T8iwLtHJEokThYL-3-G5ouGIZyzvkmiPiSWnYaYuun0</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3178549561194827564</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>深圳市优信电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FFC/FPC软排线 液晶连接线 6P 同向/反向 0.5/1.0mm间距 (6P;同向;0．5mm;20CM) x4 | FFC/FPC软排线 液晶连接线 6P 同向/反向 0.5/1.0mm间距 (6P;同向;0．5mm;40CM) x4</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=549515372213&amp;mi_id=0000TONxVuzfDqqsCnApxkm0wSEI72r53AXGsDeREaZJC0U</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -3713,44 +5592,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3199723971509827584</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1330</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>46044</v>
+          <t>3178635204854827564</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>卓悦电子让工作轻松一点点</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>细颗粒高流动性焊锡膏0402贴片qfn小封装专用强力SMT微粒含挤锡器 (套件(专用锡膏+挤锡器+6针头)) x2</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>迅维网深圳店</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=695056092174&amp;mi_id=00009HGazowYq_yqiQH9SoYTI00dZCksDsg8xfoVxJFaUT8</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x3nIQTq9ptt71miLGzzMj10</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3178635204854827564</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>卓悦电子让工作轻松一点点</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>细颗粒高流动性焊锡膏0402贴片qfn小封装专用强力SMT微粒含挤锡器 (套件(专用锡膏+挤锡器+6针头)) x2</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=695056092174&amp;mi_id=00009HGazowYq_yqiQH9SoYTI00dZCksDsg8xfoVxJFaUT8</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -3759,44 +5671,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3200239884180827648</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1478</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>46044</v>
+          <t>3178635204855827564</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>康威科技</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AD637模块有效值检波检测模块 峰值电压检测模块交流信号数据采集 (暂无) x1</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>杭州睿登科技</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源供应器 (RD6030-MAX(3.2寸2000W前级)整机) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=521661938898&amp;mi_id=0000vVe5H0E13hY2dJ_hy-yNhFpLIpFrB0LBkR1v7P-gbUs</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>124</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=781265244038&amp;mi_id=0000hbfxm3fykFbXojRRB075xjIyttyMzCLWRbSNTBQJUZA</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>交易关闭</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3178635204855827564</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>康威科技</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AD637模块有效值检波检测模块 峰值电压检测模块交流信号数据采集 (暂无) x1</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>124</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=521661938898&amp;mi_id=0000vVe5H0E13hY2dJ_hy-yNhFpLIpFrB0LBkR1v7P-gbUs</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -3805,44 +5750,77 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3199604882263827456</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>46044</v>
+          <t>3178635204856827564</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>电子采购中心</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>适用泰克鼎阳优利德示波器探头接地弹簧接地圈针示波器探头接地环 (内径4.5mm  1个) x6 | 适用泰克鼎阳优利德示波器探头接地弹簧接地圈针示波器探头接地环 (内径3.5mm  1个) x6</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>明翔科技通讯店</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=577099962185&amp;mi_id=0000BP1iumJ-537GbcyawyXszrp8KMi-oVJQ-AOdRg9abMg</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTvCt68DBJy_B0qVJMhPZRzg</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3178635204856827564</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>电子采购中心</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>适用泰克鼎阳优利德示波器探头接地弹簧接地圈针示波器探头接地环 (内径4.5mm  1个) x6 | 适用泰克鼎阳优利德示波器探头接地弹簧接地圈针示波器探头接地环 (内径3.5mm  1个) x6</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=577099962185&amp;mi_id=0000BP1iumJ-537GbcyawyXszrp8KMi-oVJQ-AOdRg9abMg</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -3851,44 +5829,77 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3196898943024827392</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>103</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>46042</v>
+          <t>3169468165118827564</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>协达兴科技</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>电子元器件配套 BOM表配单 阻容感管芯连接器电子元件一站式配单 (暂无) x430</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>文宇创新</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=714251628632&amp;mi_id=00009GTbPxqfcoqZwolE8i4SW_G-uUXUdms4S6wZfhAFDQY</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>435</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI-dnfBScWixz827TuA_MieI</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3169468165118827564</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>协达兴科技</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>电子元器件配套 BOM表配单 阻容感管芯连接器电子元件一站式配单 (暂无) x430</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>435</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=714251628632&amp;mi_id=00009GTbPxqfcoqZwolE8i4SW_G-uUXUdms4S6wZfhAFDQY</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -3897,44 +5908,77 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3196645358892827648</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>46042</v>
+          <t>3208342657476827564</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>恒脉PDU华中总店</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>加长10位12位16位PDU工业工程专用20位24超长插线板机柜插排插座 (16位【双断+防雷】2.5平方2米10A头[新国标孔]) x1</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>维修佬旗舰店</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=806839670595&amp;mi_id=00003CKKu17BY8_WER8IyWYTn6D_wLQc9dg1qEuv-joxpxg</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>183</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LfwojNceyOdm3vrTghNC2aA</t>
+          <t>买家已付款</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3208342657476827564</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>恒脉PDU华中总店</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>加长10位12位16位PDU工业工程专用20位24超长插线板机柜插排插座 (16位【双断+防雷】2.5平方2米10A头[新国标孔]) x1</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>183</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=806839670595&amp;mi_id=00003CKKu17BY8_WER8IyWYTn6D_wLQc9dg1qEuv-joxpxg</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>买家已付款</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -3943,44 +5987,77 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3191044839501827584</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>46040</v>
+          <t>3202958352610827564</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>广陆旗舰店</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>【优惠价】广陆原点数显卡尺0-150-200-300数字电子不锈钢工业文玩油标包邮 (原点0-150mm（塑胶壳+金属面板）) x1</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>七哥化妆品  护肤品</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>欧莱雅男士水能保湿酷爽水凝露50ml*3瓶=150ml爽肤水补水正品小样 (250ml[5瓶  27年后]) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=39422439278&amp;mi_id=0000JKnj5PwfY00JnuLgVBHoPgq231e-T32L4h8ZxYynCqU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>166</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=683617811077&amp;mi_id=0000rnIdNferFF2YOxDVZS6Fq8k7oXM82GA-nV2wLj-4CbQ</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3202958352610827564</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>广陆旗舰店</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>【优惠价】广陆原点数显卡尺0-150-200-300数字电子不锈钢工业文玩油标包邮 (原点0-150mm（塑胶壳+金属面板）) x1</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>166</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=39422439278&amp;mi_id=0000JKnj5PwfY00JnuLgVBHoPgq231e-T32L4h8ZxYynCqU</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -3989,44 +6066,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3188060403141827584</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>46038</v>
+          <t>3200362430879827564</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>乐清铜业</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>紫铜皮紫铜带纯紫铜薄铜箔片接地导电铜板铜带片紫铜垫片0.02-1mm (0.15mm*30mm*1米) x5</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>思壮伟业运动专营店</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>李宁运动保暖发带耳罩冬季男防寒防风护耳护额骑车跑步耳朵保护套 (☀️凛冬推荐☀️加厚针织款【耳罩/眼罩/发带三合一】) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=698854826005&amp;mi_id=0000T8iwLtHJEokThYL-3-G5or8sQH3KmSyT4JO_yB7cUHs</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>28</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=990037011548&amp;mi_id=0000VWKJmd5zBM5cexYafT3v_cf0EzAzO48Hztou0RPob_I</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3200362430879827564</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>乐清铜业</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>紫铜皮紫铜带纯紫铜薄铜箔片接地导电铜板铜带片紫铜垫片0.02-1mm (0.15mm*30mm*1米) x5</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>28</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=698854826005&amp;mi_id=0000T8iwLtHJEokThYL-3-G5or8sQH3KmSyT4JO_yB7cUHs</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -4035,44 +6145,77 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3184297068282827776</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>134.6</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>46036</v>
+          <t>3199723971509827564</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>迅维网深圳店</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>维修佬旗舰店</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1.0 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1.0 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1.0 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1.0 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1.0 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x0qGTd1YA3DQzhuKh0eQQD4</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1330</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb9mvNJZv120vXB3vHOCK8KE</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3199723971509827564</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>迅维网深圳店</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>睿登RD6030大功率数控可调直流电源锂电池充电器稳压电源 供应器 (RD6030-W(1500W前级)整机) x1</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1330</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=892134210532&amp;mi_id=0000zIWNUMcZ9Cgm5FCYHX__x0qGTd1YA3DQzhuKh0eQQD4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -4081,44 +6224,77 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3179697747085827584</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>60</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>46034</v>
+          <t>3199604882263827564</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>明翔科技通讯店</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>必兴金属</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTuiWigvxnbJiHfK_CcERvIk</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>19.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJZ-vVMgEkIXfYBOzCAlTnNM</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>卖家已发货</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3199604882263827564</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>明翔科技通讯店</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>维修佬维修免针管插针式BAG助焊膏高活性焊锡桨抗氧化助焊油TF350 (TF350助焊膏【高活性款】) x2</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=598638935331&amp;mi_id=0000-IO54-u1b21sKvcvFfMpTuiWigvxnbJiHfK_CcERvIk</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -4127,44 +6303,77 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3178956756098827776</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>46034</v>
+          <t>3196898943024827564</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>文宇创新</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>生产电源厂家</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>220V转DC12V24V1A2A1.5A2A3A4A5ALED灯带电源适配器变压器 带开关 (12V1A（电源）1米线+带开关) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI_MDFeZjV8NPXqAFG5PjQ7Q</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=708700312757&amp;mi_id=00004xBCQx384xSrpK17M3PLveisSeCKgCKdqmPR2EZOaGU</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>交易成功</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3196898943024827564</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>文宇创新</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>WY858P便携一体式恒温热风枪贴片元件拆焊利器烙铁搭档 (WY858热风枪(送托架)) x1</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>103</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=761564663178&amp;mi_id=0000FhHSKf9p1x559dVopanwI_MDFeZjV8NPXqAFG5PjQ7Q</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -4173,44 +6382,77 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3178953012990827520</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>46034</v>
+          <t>3196645358892827564</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>维修佬旗舰店</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大西洋科技视讯99</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>12V红外补光灯监控红外辅助灯大功率红外灯智能光感阵列4灯辅助灯 (12v 4灯红外常亮单独补光灯) x1.0</t>
-        </is>
+          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LXhyS72BQvbcR4MccYMdlbA</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>18.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://item.taobao.com/item.htm?id=538753635277&amp;mi_id=0000Vxky2MZksjR4DaXBHq__5Elwt7APDIpzh7gETbta5zc</t>
+          <t>交易成功</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>交易成功</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3196645358892827564</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>维修佬旗舰店</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>维修佬 补点PCB焊锡飞线手机主板USB排线苹果耳机维修线路连接 (200M*0.02MM绝缘飞线 FJ202) x1</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=543185126999&amp;mi_id=0000t_6didCuoftBt5EKQja0LXhyS72BQvbcR4MccYMdlbA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>
@@ -4219,44 +6461,156 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3178830181591827456</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="C15" s="2" t="n">
+          <t>3184297068282827564</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>维修佬旗舰店</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb3yligO3qeTIyKrLLRc83V0</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3184297068282827564</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>维修佬旗舰店</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带1.0mmx1.5米 （1卷装）) x1 | 【优惠价】维修佬 阻焊剂膏UV光固化阻焊油电路板 PCB BGA 线路板用阻焊绿油 (LVH900绿油10cc+针管助推器) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (陶瓷平口刮锡刀CS-12（单片）) x1 | 维修佬 手机维修工具 刮锡刀 锡浆刮刀 植锡手柄 锡膏刮刀片 (平口X20+多斜口X22【两片组合装】) x1 | 维修佬 手机维修焊接bga纳米透明助焊膏芯片回流焊助焊剂免洗针筒 (纯透明纳米助焊膏 ONE-X[单支装]) x1 | 维修佬超强吸锡带手机主板拆锡清洁除锡带焊锡丝吸取线吸锡线DW50 (DW50超强吸锡带2.5mmx1.5米 （1卷装）) x3</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=736183801228&amp;mi_id=0000l9rOqgazPw6XTyAHsOYCb3yligO3qeTIyKrLLRc83V0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3179697747085827564</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>必兴金属</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3179697747085827564</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>必兴金属</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>T2紫铜圆板 圆铜片 非标纯铜垫片 实心圆片 紫铜板 0.5 1 2 345mm (暂无) x1</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?id=796270860381&amp;mi_id=0000MmTmUSMTXoMqVSHv_DDHJWreKcoD7_kZws5rfp13gIQ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>交易成功</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
         <v>46034</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>大西洋科技视讯99</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>12V红外补光灯监控红外辅助灯大功率红外灯智能光感阵列4灯辅助灯 (12v 4灯红外光感单独补光灯) x1.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://item.taobao.com/item.htm?id=538753635277&amp;mi_id=0000Vxky2MZksjR4DaXBHq__5Elwt7APDIpzh7gETbta5zc</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>交易关闭</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>无匹配</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>未找到匹配发票</t>
         </is>

--- a/match_result.xlsx
+++ b/match_result.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3585,6 +3585,64 @@
       <c r="S38" t="inlineStr">
         <is>
           <t>金额一致且唯一匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6616,6 +6674,64 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>无匹配</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>未找到匹配发票</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
